--- a/hpi_scraper/NewsAnnouncements/tavily/tavily_data.xlsx
+++ b/hpi_scraper/NewsAnnouncements/tavily/tavily_data.xlsx
@@ -445,7 +445,7 @@
   <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="42" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
@@ -518,37 +518,37 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Singapore Telecommunications</t>
+          <t>Sea Limited</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>singtel.com</t>
+          <t>sea.com</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/singtel</t>
+          <t>https://www.linkedin.com/company/sea-ltd</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Singtel logs 14% rise in underlying profit on Optus, regional partners' boost - Reuters</t>
+          <t>Singapore's Carro eyes M&amp;A, Australia foray ahead of potential dual listing - Reuters</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Singtel logs 14% rise in underlying profit on Optus, regional partners' boost - Reuters</t>
+          <t>Singapore's Carro eyes M&amp;A, Australia foray ahead of potential dual listing - Reuters</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/world/asia-pacific/singtels-first-half-underlying-profit-rises-14-2025-11-11/</t>
+          <t>https://www.reuters.com/business/autos-transportation/singapores-carro-eyes-ma-australia-foray-ahead-potential-dual-listing-2025-09-12/</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -559,7 +559,7 @@
       <c r="I2" s="3" t="inlineStr"/>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -571,48 +571,48 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Singapore Telecommunications</t>
+          <t>Sea Limited</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>singtel.com</t>
+          <t>sea.com</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/singtel</t>
+          <t>https://www.linkedin.com/company/sea-ltd</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Freeport-McMoRan (FCX) Moves 15.5% Higher: Will This Strength Last? - Yahoo.co</t>
+          <t>Medialink Group Launches Japan Subsidiary - Variety</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Freeport-McMoRan (FCX) Moves 15.5% Higher: Will This Strength Last? - Yahoo.co</t>
+          <t>Medialink Group Launches Japan Subsidiary - Variety</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>https://sg.finance.yahoo.com/news/first-quantum-minerals-q2-earnings-211325439.html</t>
+          <t>https://variety.com/2025/tv/news/medialink-japan-subsidiary-1236521270/</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>expansion</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -624,48 +624,48 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Singapore Telecommunications</t>
+          <t>Sea Limited</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>singtel.com</t>
+          <t>sea.com</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/singtel</t>
+          <t>https://www.linkedin.com/company/sea-ltd</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Singtel profit increases by 14% amid Airtel stake sale - Telecoms.com</t>
+          <t>Sea, Pole Star Global Collaborate to Manage Evolving Regulations - Marine News Magazine</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Singtel profit increases by 14% amid Airtel stake sale - Telecoms.com</t>
+          <t>Sea, Pole Star Global Collaborate to Manage Evolving Regulations - Marine News Magazine</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>https://www.telecoms.com/communications-service-provider/singtel-profit-increases-by-14-amid-airtel-stake-sale</t>
+          <t>https://www.marinelink.com/news/sea-pole-star-global-collaborate-manage-531342</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>expansion</t>
+          <t>other</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -677,48 +677,48 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Singapore Telecommunications</t>
+          <t>Sea Limited</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>singtel.com</t>
+          <t>sea.com</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/singtel</t>
+          <t>https://www.linkedin.com/company/sea-ltd</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Singtel expands enterprise push with Brazil office opening - Developing Telecoms</t>
+          <t>American Airlines CEO Rejects United Merger, Hints At Alaska Deal - Live and Let's Fly</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Singtel expands enterprise push with Brazil office opening - Developing Telecoms</t>
+          <t>American Airlines CEO Rejects United Merger, Hints At Alaska Deal - Live and Let's Fly</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>https://www.developingtelecoms.com/telecom-business/operator-news/19723-singtel-expands-enterprise-push-with-brazil-office-opening.html</t>
+          <t>https://liveandletsfly.com/american-airlines-rejects-united-merger-alaska-deal/</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>expansion</t>
+          <t>leadership</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -730,48 +730,48 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Singapore Telecommunications</t>
+          <t>Sea Limited</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>singtel.com</t>
+          <t>sea.com</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/singtel</t>
+          <t>https://www.linkedin.com/company/sea-ltd</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Big-ticket deals lift Singapore M&amp;A as volumes fall - Asian Business Review</t>
+          <t>Clear Channel Outdoor Holdings, Inc. Agrees to be Acquired by Mubadala Capital, in Partnership with TWG Global, for $6.2 Billion - PR Newswire</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Big-ticket deals lift Singapore M&amp;A as volumes fall - Asian Business Review</t>
+          <t>Clear Channel Outdoor Holdings, Inc. Agrees to be Acquired by Mubadala Capital, in Partnership with TWG Global, for $6.2 Billion - PR Newswire</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>https://asianbusinessreview.com/exclusive/big-ticket-deals-lift-singapore-ma-volumes-fall</t>
+          <t>https://www.prnewswire.com/news-releases/clear-channel-outdoor-holdings-inc-agrees-to-be-acquired-by-mubadala-capital-in-partnership-with-twg-global-for-6-2-billion-302683053.html</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>M&amp;A</t>
+          <t>launch</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
